--- a/reports/播客监控日报_2026-03-11.xlsx
+++ b/reports/播客监控日报_2026-03-11.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>171376</v>
+        <v>171477</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -544,27 +544,27 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>133</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:34</t>
+          <t>2026-03-11 14:43:17</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>73443</v>
+        <v>73523</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -604,27 +604,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:36</t>
+          <t>2026-03-11 14:43:19</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>36395</v>
+        <v>36425</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -694,277 +694,277 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:38</t>
+          <t>2026-03-11 14:43:21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>与财同行</t>
+          <t>人间钱话</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>财通基金</t>
+          <t>天弘基金</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1301</v>
+        <v>26804</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
+          <t>E34 黄金白银巨震后的大宗时代线索</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1:29:38</t>
+          <t>1:39:04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:40</t>
+          <t>2026-03-11 14:43:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>人间钱话</t>
+          <t>深度求真</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>天弘基金</t>
+          <t>大成基金</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>26798</v>
+        <v>20462</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>E34 黄金白银巨震后的大宗时代线索</t>
+          <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>131</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>307</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1:39:04</t>
+          <t>44:50</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:42</t>
+          <t>2026-03-11 14:43:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>深度求真</t>
+          <t>德邦基金财经列车</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>大成基金</t>
+          <t>德邦基金</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>20461</v>
+        <v>8371</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
+          <t>305.3月10日财经速递</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44:50</t>
+          <t>3:42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:44</t>
+          <t>2026-03-11 14:43:37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>养基方程式</t>
+          <t>茶水间经济学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>广发基金</t>
+          <t>易方达基金</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3297</v>
+        <v>6809</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
+          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>55:16</t>
+          <t>1:42:13</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:46</t>
+          <t>2026-03-11 14:43:47</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>基金经理一周论市</t>
+          <t>随基漫步 Random Walk</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>兴全基金</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>303</v>
+        <v>6499</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
+          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -974,302 +974,302 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2:01</t>
+          <t>55:15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:48</t>
+          <t>2026-03-11 14:43:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>好朋友</t>
+          <t>泰客Talk</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>中泰资管</t>
+          <t>国泰基金</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>50</v>
+        <v>6142</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
+          <t>Vol 26 低利率时代启示录，从渡边太太的故事聊起</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>338</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1:00:18</t>
+          <t>43:01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:50</t>
+          <t>2026-03-11 14:43:45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>好朋友的直播间</t>
+          <t>时间嘉讲</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>中泰资管</t>
+          <t>嘉实基金</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1587</v>
+        <v>5356</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
+          <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>501</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32:01</t>
+          <t>1:20:43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:52</t>
+          <t>2026-03-11 14:43:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>德邦基金财经列车</t>
+          <t>莫问钱程</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>德邦基金</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>8372</v>
+        <v>4464</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>305.3月10日财经速递</t>
+          <t>养娃这条路，做好财务规划能省多少弯路？</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3:42</t>
+          <t>1:12:50</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:54</t>
+          <t>2026-03-11 14:43:49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>投资心得·基金聊天局</t>
+          <t>财话连篇</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>国投瑞银基金</t>
+          <t>易方达基金</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1489</v>
+        <v>3810</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>EP9.别内耗了，允许自己“知行不合一”</t>
+          <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1:10:07</t>
+          <t>25:02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:56</t>
+          <t>2026-03-11 14:43:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>投资心法</t>
+          <t>养基方程式</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>国投瑞银基金</t>
+          <t>广发基金</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>28</v>
+        <v>3297</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0010 段永平《波士堂》访谈：敢为天下后</t>
+          <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1279,357 +1279,357 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>55:16</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:51:58</t>
+          <t>2026-03-11 14:43:29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>时间嘉讲</t>
+          <t>钱途规划局</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>嘉实基金</t>
+          <t>汇添富基金</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>5354</v>
+        <v>1975</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
+          <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1:20:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:00</t>
+          <t>2026-03-11 14:43:53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>泰客Talk</t>
+          <t>好朋友的直播间</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>国泰基金</t>
+          <t>中泰资管</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6141</v>
+        <v>1588</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Vol 26 低利率时代启示录，从渡边太太的故事聊起</t>
+          <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43:01</t>
+          <t>32:01</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:02</t>
+          <t>2026-03-11 14:43:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>茶水间经济学</t>
+          <t>投资心得·基金聊天局</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>易方达基金</t>
+          <t>国投瑞银基金</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>6810</v>
+        <v>1490</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
+          <t>EP9.别内耗了，允许自己“知行不合一”</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1:42:13</t>
+          <t>1:10:07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:04</t>
+          <t>2026-03-11 14:43:39</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>莫问钱程</t>
+          <t>与财同行</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>财通基金</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4464</v>
+        <v>1301</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>养娃这条路，做好财务规划能省多少弯路？</t>
+          <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1:12:50</t>
+          <t>1:29:38</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:06</t>
+          <t>2026-03-11 14:43:23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>财话连篇</t>
+          <t>鹏然心动</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>易方达基金</t>
+          <t>鹏华基金</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3810</v>
+        <v>734</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
+          <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>151</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25:02</t>
+          <t>54:38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:08</t>
+          <t>2026-03-11 14:43:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>钱途规划局</t>
+          <t>基金经理一周论市</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>汇添富基金</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1975</v>
+        <v>303</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
+          <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1639,142 +1639,142 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>2:01</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:10</t>
+          <t>2026-03-11 14:43:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>随基漫步 Random Walk</t>
+          <t>好朋友</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>兴全基金</t>
+          <t>中泰资管</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6476</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>OpenClaw爆火后，AI发展的2个重点方向</t>
+          <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>55:15</t>
+          <t>1:00:18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:12</t>
+          <t>2026-03-11 14:43:33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>鹏然心动</t>
+          <t>投资心法</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>鹏华基金</t>
+          <t>国投瑞银基金</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>734</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
+          <t>0010 段永平《波士堂》访谈：敢为天下后</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>54:38</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:52:14</t>
+          <t>2026-03-11 14:43:41</t>
         </is>
       </c>
     </row>
